--- a/artfynd/A 26958-2024 artfynd.xlsx
+++ b/artfynd/A 26958-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118301797</v>
+        <v>118302135</v>
       </c>
       <c r="B5" t="n">
-        <v>56502</v>
+        <v>78484</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,48 +1036,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494214</v>
+        <v>494253</v>
       </c>
       <c r="R5" t="n">
-        <v>6932359</v>
+        <v>6932329</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118302135</v>
+        <v>118301710</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>74580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1148,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494253</v>
+        <v>494208</v>
       </c>
       <c r="R6" t="n">
-        <v>6932329</v>
+        <v>6932398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118301710</v>
+        <v>118301797</v>
       </c>
       <c r="B7" t="n">
-        <v>74580</v>
+        <v>56502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,34 +1264,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494208</v>
+        <v>494214</v>
       </c>
       <c r="R7" t="n">
-        <v>6932398</v>
+        <v>6932359</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 26958-2024 artfynd.xlsx
+++ b/artfynd/A 26958-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118302135</v>
+        <v>118301710</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>74580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,25 +1036,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494253</v>
+        <v>494208</v>
       </c>
       <c r="R5" t="n">
-        <v>6932329</v>
+        <v>6932398</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118301710</v>
+        <v>118302135</v>
       </c>
       <c r="B6" t="n">
-        <v>74580</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,25 +1148,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494208</v>
+        <v>494253</v>
       </c>
       <c r="R6" t="n">
-        <v>6932398</v>
+        <v>6932329</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 26958-2024 artfynd.xlsx
+++ b/artfynd/A 26958-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118301710</v>
+        <v>118302135</v>
       </c>
       <c r="B5" t="n">
-        <v>74580</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,25 +1036,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494208</v>
+        <v>494253</v>
       </c>
       <c r="R5" t="n">
-        <v>6932398</v>
+        <v>6932329</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118302135</v>
+        <v>118301710</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>74587</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,25 +1148,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494253</v>
+        <v>494208</v>
       </c>
       <c r="R6" t="n">
-        <v>6932329</v>
+        <v>6932398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118301797</v>
+        <v>118301840</v>
       </c>
       <c r="B7" t="n">
-        <v>56502</v>
+        <v>74603</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,48 +1260,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494214</v>
+        <v>494261</v>
       </c>
       <c r="R7" t="n">
-        <v>6932359</v>
+        <v>6932279</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,6 +1345,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118301840</v>
+        <v>118301797</v>
       </c>
       <c r="B8" t="n">
-        <v>74596</v>
+        <v>56502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,41 +1376,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494261</v>
+        <v>494214</v>
       </c>
       <c r="R8" t="n">
-        <v>6932279</v>
+        <v>6932359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1468,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26958-2024 artfynd.xlsx
+++ b/artfynd/A 26958-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118205373</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gillån (Gillån), Jmt</t>
+          <t>Gillån, Gillån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -912,7 +912,7 @@
         <v>118230024</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 26958-2024 artfynd.xlsx
+++ b/artfynd/A 26958-2024 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 26958-2024 artfynd.xlsx
+++ b/artfynd/A 26958-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118205373</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>118230024</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 26958-2024 artfynd.xlsx
+++ b/artfynd/A 26958-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118205373</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>118230024</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
